--- a/group-travel-split/chia-tien-chuyen-di.xlsx
+++ b/group-travel-split/chia-tien-chuyen-di.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,12 +75,6 @@
       <b val="1"/>
       <color rgb="001F3B4D"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="000000FF"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -169,7 +163,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -535,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -659,6 +653,14 @@
       </c>
       <c r="E6" s="11" t="n"/>
       <c r="F6" s="11" t="n"/>
+      <c r="H6" s="8" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Tú ứng trả bữa BBQ</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -680,6 +682,14 @@
       </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
+      <c r="H7" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Việt ứng trả bữa BBQ</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -750,12 +760,13 @@
           <t>Ăn tối BBQ</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>2100000</v>
+      <c r="B11" s="10">
+        <f>$H$6+$H$7</f>
+        <v/>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Tú 1.100.000 · Việt 1.000.000</t>
+          <t>Tú và Việt ứng trả</t>
         </is>
       </c>
       <c r="D11" s="10">
@@ -867,7 +878,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Mọi người đóng cho Chi, Chi bank lại phần đã ứng cho Việt &amp; Tú.</t>
+          <t>Tú và Việt không phải đóng — tiền hai bạn ứng đang dư.</t>
         </is>
       </c>
     </row>
@@ -881,6 +892,11 @@
         <f>$F$15</f>
         <v/>
       </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>phần còn thiếu</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -892,6 +908,11 @@
         <f>$F$15</f>
         <v/>
       </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>phần còn thiếu</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -903,72 +924,57 @@
         <f>$F$15</f>
         <v/>
       </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>phần còn thiếu</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Việt  →  Chi</t>
-        </is>
-      </c>
-      <c r="B22" s="19">
-        <f>$F$15</f>
-        <v/>
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Chi  →  Tú</t>
+        </is>
+      </c>
+      <c r="B22" s="20">
+        <f>$H$6-$F$15</f>
+        <v/>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>đã ứng 1.100.000 cho BBQ → đang dư, nhận lại phần chênh</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Tú  →  Chi</t>
-        </is>
-      </c>
-      <c r="B23" s="19">
-        <f>$F$15</f>
-        <v/>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Chi  →  Việt</t>
+        </is>
+      </c>
+      <c r="B23" s="20">
+        <f>$H$7-$F$15</f>
+        <v/>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>đã ứng 1.000.000 cho BBQ → đang dư, nhận lại phần chênh</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Chi  →  Tú</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>hoàn lại tiền đã ứng trả bữa BBQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Chi  →  Việt</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>hoàn lại tiền đã ứng trả bữa BBQ</t>
-        </is>
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Chi thực nhận</t>
+        </is>
+      </c>
+      <c r="B24" s="16">
+        <f>SUM(B19:B21)-SUM(B22:B23)</f>
+        <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Chi thực nhận</t>
-        </is>
-      </c>
-      <c r="B26" s="16">
-        <f>SUM(B19:B23)-SUM(B24:B25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Giả định: tiền cọc gom thành quỹ chung do Chi giữ và Chi dùng để thanh toán. Nếu cọc nộp cho bên khác thì cách chốt sẽ khác.</t>
         </is>
